--- a/Sample Data/ITEMS-SAMPLE.xlsx
+++ b/Sample Data/ITEMS-SAMPLE.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t xml:space="preserve">PART NO</t>
   </si>
@@ -95,6 +95,15 @@
   </si>
   <si>
     <t xml:space="preserve">2W8003JR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLK-320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINK-GROUP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMC</t>
   </si>
 </sst>
 </file>
@@ -373,7 +382,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -502,6 +511,17 @@
         <v>13</v>
       </c>
     </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
